--- a/data_input/monthly/2025-11.xlsx
+++ b/data_input/monthly/2025-11.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="_HƯỚNG DẪN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="voucher_month" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="booking" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="voucher_month" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -622,12 +623,26 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   voucher_month              2 dòng   bắt buộc: m, brand</t>
+          <t xml:space="preserve">   booking                   17 dòng   bắt buộc: month, status</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                  Booking tiệc &amp; sự kiện — gộp theo tháng NHẬN LEAD (month) × tháng DIỄN RA (ev_month) × cửa hàng × phân khúc × loại × nguồn × trạng thái. month = Inquiry Date → Input Date → (thiếu cả hai) ngày sự kiện, khi đó inq_est đếm số lead bị ước. seg ∈ event|table, stage ∈ won|open|lost — luật ở $booking. exp chỉ cộng ô có số (exp_n lead); ô trống/TBA KHÔNG tính là 0. closed_n = số lead Confirmed đã nhập Closed Revenue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   voucher_month              2 dòng   bắt buộc: m, brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">                                  Voucher đã dùng theo tháng × brand.</t>
         </is>
@@ -639,6 +654,1373 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>ev_month</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>outlet</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>etype</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>stage</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>lost_reason</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>leads</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>guests</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>exp</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>exp_n</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>closed_n</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>inq_est</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M2" t="n">
+        <v>59</v>
+      </c>
+      <c r="N2" t="n">
+        <v>14874341</v>
+      </c>
+      <c r="O2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P2" t="n">
+        <v>14874341</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>101</v>
+      </c>
+      <c r="N3" t="n">
+        <v>100425000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>700</v>
+      </c>
+      <c r="N4" t="n">
+        <v>239890973</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>239890973</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>70</v>
+      </c>
+      <c r="N5" t="n">
+        <v>71949000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>65</v>
+      </c>
+      <c r="N6" t="n">
+        <v>50900817</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>50900817</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Room rental</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>100</v>
+      </c>
+      <c r="N7" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>30</v>
+      </c>
+      <c r="N8" t="n">
+        <v>29227208</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>29227208</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>25</v>
+      </c>
+      <c r="N9" t="n">
+        <v>25896336</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>25896336</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Room rental</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N10" t="n">
+        <v>23360000</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>30</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20053866</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>20053866</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Workshop</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>15</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20020736</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>20020736</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Room rental</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>60</v>
+      </c>
+      <c r="N13" t="n">
+        <v>11555000</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>11555000</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>16</v>
+      </c>
+      <c r="N14" t="n">
+        <v>7334000</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>7334000</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Chụp hình / quay</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Hotline</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Room rental</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Lost</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Không gian / sức chứa</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>80</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>NOIRE DINING</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>60</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>NOIRE ET</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Room + Lunch</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>MKT</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>12</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/data_input/monthly/2025-11.xlsx
+++ b/data_input/monthly/2025-11.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,8 +35,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00F3F2EE"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +57,11 @@
         <fgColor rgb="FFF2EFE6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F1F26"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -66,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -78,6 +87,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2028,36 +2038,29 @@
   </sheetPr>
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>used</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>rev</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>disc</t>
         </is>

--- a/data_input/monthly/2025-11.xlsx
+++ b/data_input/monthly/2025-11.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="_HƯỚNG DẪN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="booking" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="voucher_month" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_HƯỚNG DẪN" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="booking" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="voucher_month" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data_input/monthly/2025-11.xlsx
+++ b/data_input/monthly/2025-11.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,12 +35,8 @@
     <font>
       <b val="1"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00F3F2EE"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -57,11 +53,6 @@
         <fgColor rgb="FFF2EFE6"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F1F26"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -75,7 +66,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -87,7 +78,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2038,29 +2028,36 @@
   </sheetPr>
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>used</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>rev</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>disc</t>
         </is>
